--- a/excel/Security_Report.xlsx
+++ b/excel/Security_Report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>Category</t>
   </si>
@@ -28,45 +28,6 @@
     <t>Details</t>
   </si>
   <si>
-    <t>Security Headers</t>
-  </si>
-  <si>
-    <t>Header Check: x-frame-options</t>
-  </si>
-  <si>
-    <t>WARNING</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>Missing recommended security header: x-frame-options</t>
-  </si>
-  <si>
-    <t>Header Check: x-content-type-options</t>
-  </si>
-  <si>
-    <t>Missing recommended security header: x-content-type-options</t>
-  </si>
-  <si>
-    <t>Header Check: content-security-policy</t>
-  </si>
-  <si>
-    <t>Missing recommended security header: content-security-policy</t>
-  </si>
-  <si>
-    <t>Header Check: strict-transport-security</t>
-  </si>
-  <si>
-    <t>Missing recommended security header: strict-transport-security</t>
-  </si>
-  <si>
-    <t>Header Check: referrer-policy</t>
-  </si>
-  <si>
-    <t>Missing recommended security header: referrer-policy</t>
-  </si>
-  <si>
     <t>XSS Protection</t>
   </si>
   <si>
@@ -121,22 +82,22 @@
     <t>CORS Configuration</t>
   </si>
   <si>
-    <t>Wildcard Origin Check</t>
+    <t>Origin Restriction Check</t>
   </si>
   <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>Access-Control-Allow-Origin: Not specified</t>
+    <t>CORS origin restricted appropriately.</t>
   </si>
   <si>
     <t>Access Control</t>
   </si>
   <si>
-    <t>Unauthenticated Request to Protected Route</t>
-  </si>
-  <si>
-    <t>Protected endpoint returned HTTP status 404</t>
+    <t>Unauthenticated Request Check</t>
+  </si>
+  <si>
+    <t>Unauthorized request correctly rejected.</t>
   </si>
 </sst>
 </file>
@@ -523,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -602,172 +563,87 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s">
-        <v>8</v>
-      </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
         <v>21</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" t="s">
         <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
